--- a/output/pdf_financials_xlsx/QCA.xlsx
+++ b/output/pdf_financials_xlsx/QCA.xlsx
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.395568</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.486187</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.311164</v>
       </c>
     </row>
     <row r="93">
@@ -2966,7 +2966,11 @@
           <t>Share-based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.395568</v>
       </c>

--- a/output/pdf_financials_xlsx/QCA.xlsx
+++ b/output/pdf_financials_xlsx/QCA.xlsx
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.067428</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.001545</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.043767</v>
       </c>
     </row>
     <row r="65">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.090922</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.124149</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.062022</v>
       </c>
     </row>
     <row r="68">
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.205214</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.181905</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.044999</v>
       </c>
     </row>
     <row r="122">
@@ -3640,7 +3640,11 @@
           <t>Repurchase of common shares (Note 7)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.205214</v>
       </c>
